--- a/outputs/yogurt_dessert/silpo_novus/primary_chain_output.xlsx
+++ b/outputs/yogurt_dessert/silpo_novus/primary_chain_output.xlsx
@@ -23,7 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -62,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +503,11 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>cointegration_p</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pair_n_obs</t>
         </is>
       </c>
     </row>
@@ -538,6 +547,7 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -575,6 +585,7 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,15 +593,27 @@
           <t>retail</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>5.695496839419695e-10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.468661222075579e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.005113444428569e-05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>I(0)</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -612,6 +635,7 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,6 +671,9 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -682,6 +709,9 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -717,6 +747,9 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -852,7 +885,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -876,7 +909,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -999,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,6 +1074,1776 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>combined_rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>51.39</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>52.695</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>52.695</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45963</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45970</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>49.4675</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>37.24</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>54.695</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>41.365</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>146.4825</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>37.49</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>49.845</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45998</v>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>47.98999999999999</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>55.695</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>37.195</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>37.49</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>yogurt_dessert</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>silpo_novus</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>promo_controlled</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>daily_median_of_available_silpo_novus</t>
         </is>
       </c>
     </row>
@@ -1068,7 +2871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,10 +2912,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>n_obs_producer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_obs_prozorro</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>n_obs_retail</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>n_obs_pair_prod_prozorro</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>n_obs_pair_prozorro_retail</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>any_i2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>eligibility_note</t>
         </is>
@@ -1136,7 +2964,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1151,15 +2979,30 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>I(0)</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Insufficient common sample after alignment; model outputs are placeholders.</t>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>59</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Low pair overlap in main chain links (min pair n_obs=0). Daily estimation kept; long-run identification may be weak.</t>
         </is>
       </c>
     </row>

--- a/outputs/yogurt_dessert/silpo_novus/primary_chain_output.xlsx
+++ b/outputs/yogurt_dessert/silpo_novus/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,7 +606,7 @@
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.005113444428569e-05</v>
+        <v>1.005113444428642e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.1</v>
